--- a/downloads/delhi.xlsx
+++ b/downloads/delhi.xlsx
@@ -1304,7 +1304,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SULTAN PUR MAJRA (SC)</t>
+          <t>Sultan Pur Majra (SC)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
